--- a/tame_output/MOZAIC/data/universe_last2023-07-29.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-07-29.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.9437120281347</v>
+        <v>569.6291690750669</v>
       </c>
       <c r="E2" t="n">
-        <v>10018.45466331147</v>
+        <v>8092.26819733258</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6196763230413709</v>
+        <v>0.6184164861523787</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4977388138485235</v>
+        <v>0.4977419276272899</v>
       </c>
       <c r="H2" t="n">
-        <v>1.244982922368511</v>
+        <v>1.242444029379518</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.4498065929988</v>
+        <v>225.1127500341888</v>
       </c>
       <c r="E3" t="n">
-        <v>3446.144886940226</v>
+        <v>2706.614991854989</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2654583054619142</v>
+        <v>0.2656038980228468</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5967349704942067</v>
+        <v>0.5967346487120421</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4448512632703019</v>
+        <v>0.4450954852313521</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907138015495225</v>
+        <v>0.8907123119243963</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067869451403068</v>
+        <v>1.067860409295674</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.53099725907202</v>
+        <v>37.33431390723969</v>
       </c>
       <c r="E4" t="n">
-        <v>836.6298065946012</v>
+        <v>745.0536150128784</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7776500157345041</v>
+        <v>0.7678968287942489</v>
       </c>
       <c r="G4" t="n">
-        <v>1.106497374776316</v>
+        <v>1.106525945986719</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7028033084052366</v>
+        <v>0.6939709200487788</v>
       </c>
       <c r="I4" t="n">
         <v>0.3422195892575038</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.473591803358084</v>
+        <v>0.4736045970124777</v>
       </c>
       <c r="N4" t="n">
-        <v>1.052817406542015</v>
+        <v>1.052866446736842</v>
       </c>
     </row>
     <row r="5">
@@ -675,10 +675,10 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.19646540658244</v>
+        <v>37.20735613601534</v>
       </c>
       <c r="E5" t="n">
-        <v>346.0119448330558</v>
+        <v>296.6463062016474</v>
       </c>
       <c r="F5" t="n">
         <v>-0.3304734978823504</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.7362510657835305</v>
+        <v>0.736245785318245</v>
       </c>
       <c r="N5" t="n">
-        <v>0.8289634244059252</v>
+        <v>0.8289522931982394</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.93338449454299</v>
+        <v>10.94134259497625</v>
       </c>
       <c r="E6" t="n">
-        <v>333.719019990539</v>
+        <v>292.1664960176109</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4806897526753747</v>
+        <v>-0.4801515811336715</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8128073896407123</v>
+        <v>0.8128225576359793</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.591394417425087</v>
+        <v>-0.5907212793529609</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6677431918878259</v>
+        <v>0.6676987609534717</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090424507086712</v>
+        <v>1.090365477539126</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.88797076507893</v>
+        <v>10.89389171443818</v>
       </c>
       <c r="E7" t="n">
-        <v>159.2284451008576</v>
+        <v>138.6164214039966</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3007826795216272</v>
+        <v>-0.3013884339006002</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7130885212952833</v>
+        <v>0.7130846684404449</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4218027222977495</v>
+        <v>-0.4226544858407251</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7508941799012498</v>
+        <v>0.7508914919593781</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075773087203866</v>
+        <v>1.075756694098613</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>10.15541212330588</v>
+        <v>10.12614433688922</v>
       </c>
       <c r="E8" t="n">
-        <v>351.0579748141134</v>
+        <v>304.2440739704264</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2945134163802088</v>
+        <v>-0.2971589171955368</v>
       </c>
       <c r="G8" t="n">
-        <v>1.169472115979098</v>
+        <v>1.169439719534516</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2518344921235152</v>
+        <v>-0.2541036636876144</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.737408396529189</v>
+        <v>0.7374238852983269</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732592544193652</v>
+        <v>1.732570100558365</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.529180459072125</v>
+        <v>7.521557157283191</v>
       </c>
       <c r="E9" t="n">
-        <v>211.1973353577184</v>
+        <v>200.8559237962901</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4651739957011893</v>
+        <v>0.4639993406469634</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4802452515869484</v>
+        <v>0.4802684902471621</v>
       </c>
       <c r="H9" t="n">
-        <v>0.9686175847945258</v>
+        <v>0.9661248865362245</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6771818671335971</v>
+        <v>0.6771973334745831</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6533815870961306</v>
+        <v>0.6534240394367173</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.696671820495119</v>
+        <v>6.688483437168286</v>
       </c>
       <c r="E10" t="n">
-        <v>295.3870511161902</v>
+        <v>260.293630285515</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9730162025321596</v>
+        <v>0.9706832171795137</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8199200782156884</v>
+        <v>0.8199297718847482</v>
       </c>
       <c r="H10" t="n">
-        <v>1.186720789481872</v>
+        <v>1.183861411628258</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.66431495401674</v>
+        <v>0.6643215532394263</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094319257213926</v>
+        <v>1.094336219981039</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.637210406881151</v>
+        <v>6.683446675339108</v>
       </c>
       <c r="E11" t="n">
-        <v>200.2113118722286</v>
+        <v>196.9317698332213</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2745711762536331</v>
+        <v>-0.2654894672356645</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9566660907681243</v>
+        <v>0.9567601997649586</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2870083709491313</v>
+        <v>-0.2774879926034607</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133760268309194</v>
+        <v>0.7132372146160029</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371126052154183</v>
+        <v>1.370985528964298</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.387105911047588</v>
+        <v>6.511303035251381</v>
       </c>
       <c r="E12" t="n">
-        <v>84.13970464545577</v>
+        <v>71.95166005517871</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2695471562137495</v>
+        <v>-0.2702976349893856</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6571915590217076</v>
+        <v>0.657184595113551</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4101500582493728</v>
+        <v>-0.4112963648252931</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7887942502802191</v>
+        <v>0.7887934190483089</v>
       </c>
       <c r="N12" t="n">
-        <v>1.041487841948322</v>
+        <v>1.041469193074815</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.673084444716476</v>
+        <v>4.673459338621165</v>
       </c>
       <c r="E13" t="n">
-        <v>132.9884578444517</v>
+        <v>133.8528116731166</v>
       </c>
       <c r="F13" t="n">
-        <v>1.695160297037463</v>
+        <v>1.696672281681196</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8595799152431924</v>
+        <v>0.8595747570457376</v>
       </c>
       <c r="H13" t="n">
-        <v>1.972079927621236</v>
+        <v>1.973850753263705</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6033791788018757</v>
+        <v>0.6033908606970946</v>
       </c>
       <c r="N13" t="n">
-        <v>1.042017638455386</v>
+        <v>1.042025040887648</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.566295058800276</v>
+        <v>4.569562712479554</v>
       </c>
       <c r="E14" t="n">
-        <v>72.98602849285778</v>
+        <v>59.60660031404982</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4002737205448371</v>
+        <v>-0.399661244723583</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8487128520055447</v>
+        <v>0.8487110939944503</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4716244364616056</v>
+        <v>-0.4709037593023337</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601995023913785</v>
+        <v>0.7601942128233039</v>
       </c>
       <c r="N14" t="n">
-        <v>1.296244274741518</v>
+        <v>1.296224461316894</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.360500136566328</v>
+        <v>4.352930923947733</v>
       </c>
       <c r="E15" t="n">
-        <v>200.816313745577</v>
+        <v>139.2397603388122</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6263024873397858</v>
+        <v>0.6208185665124759</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9589191299546058</v>
+        <v>0.9589340242295933</v>
       </c>
       <c r="H15" t="n">
-        <v>0.653133791761391</v>
+        <v>0.6474048796122768</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.513839907269534</v>
+        <v>0.5138496894002961</v>
       </c>
       <c r="N15" t="n">
-        <v>0.989938705010876</v>
+        <v>0.9899667340757415</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.179085623686471</v>
+        <v>4.1737395151662</v>
       </c>
       <c r="E16" t="n">
-        <v>165.1387587525906</v>
+        <v>144.6210579683855</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.01676292647512223</v>
+        <v>-0.01590944401669769</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7928206083437976</v>
+        <v>0.79281853512399</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0211434040673337</v>
+        <v>-0.02006694257496085</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.713696567302036</v>
+        <v>0.7136933310971952</v>
       </c>
       <c r="N16" t="n">
-        <v>1.136807761255846</v>
+        <v>1.136792522152029</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.514834760336149</v>
+        <v>3.532561665459022</v>
       </c>
       <c r="E17" t="n">
-        <v>61.31952945416636</v>
+        <v>62.71265972812335</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1640489652329972</v>
+        <v>-0.1564638376417425</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7524357627079322</v>
+        <v>0.7526380777115468</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.2180238810587674</v>
+        <v>-0.2078872200001928</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7236732611081168</v>
+        <v>0.7233909338090679</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093982681324377</v>
+        <v>1.093843077378252</v>
       </c>
     </row>
     <row r="18">
@@ -1377,10 +1377,10 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.131627623519747</v>
+        <v>3.12999967221058</v>
       </c>
       <c r="E18" t="n">
-        <v>49.65819003369008</v>
+        <v>44.45120320060639</v>
       </c>
       <c r="F18" t="n">
         <v>-0.4627272967355784</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644755107469279</v>
+        <v>0.7644678671257165</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143514437505815</v>
+        <v>1.143495850520384</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.978330944207317</v>
+        <v>2.982965818383045</v>
       </c>
       <c r="E19" t="n">
-        <v>95.67965386396985</v>
+        <v>90.99662319870038</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1178453437360669</v>
+        <v>0.1215529805621487</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4803930118195091</v>
+        <v>0.4803761620205573</v>
       </c>
       <c r="H19" t="n">
-        <v>0.245310278952066</v>
+        <v>0.2530370783822261</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7177578145744903</v>
+        <v>0.7177589255860536</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6927445252548915</v>
+        <v>0.6927169659438657</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.631572079692982</v>
+        <v>2.628786383079984</v>
       </c>
       <c r="E20" t="n">
-        <v>83.91043273561445</v>
+        <v>77.15182648684522</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3049664896394392</v>
+        <v>-0.3059777697932441</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7769090422339894</v>
+        <v>0.7769056949965608</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3925382162659775</v>
+        <v>-0.3938415843310282</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7325892438370996</v>
+        <v>0.7325917449641626</v>
       </c>
       <c r="N20" t="n">
-        <v>1.143481665373225</v>
+        <v>1.143473489330619</v>
       </c>
     </row>
   </sheetData>
